--- a/data/BELL.MI.xlsx
+++ b/data/BELL.MI.xlsx
@@ -25166,6 +25166,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1079">
+      <c r="A1079" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1079" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1079" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="D1079" t="n">
+        <v>4.01999998092651</v>
+      </c>
+      <c r="E1079" t="n">
+        <v>4.01999998092651</v>
+      </c>
+      <c r="F1079" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="G1079" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BELL.MI.xlsx
+++ b/data/BELL.MI.xlsx
@@ -25189,6 +25189,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1080">
+      <c r="A1080" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1080" t="n">
+        <v>17000</v>
+      </c>
+      <c r="C1080" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="D1080" t="n">
+        <v>3.92000007629395</v>
+      </c>
+      <c r="E1080" t="n">
+        <v>4.07999992370605</v>
+      </c>
+      <c r="F1080" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G1080" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BELL.MI.xlsx
+++ b/data/BELL.MI.xlsx
@@ -25200,7 +25200,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="D1080" t="n">
-        <v>3.92000007629395</v>
+        <v>3.90000009536743</v>
       </c>
       <c r="E1080" t="n">
         <v>4.07999992370605</v>
@@ -25209,6 +25209,29 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1080" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1081" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1081" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1081" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="E1081" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="F1081" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1081" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BELL.MI.xlsx
+++ b/data/BELL.MI.xlsx
@@ -25235,6 +25235,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1082">
+      <c r="A1082" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1082" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C1082" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="D1082" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="E1082" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="F1082" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="G1082" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BELL.MI.xlsx
+++ b/data/BELL.MI.xlsx
@@ -25076,22 +25076,22 @@
     </row>
     <row r="1075">
       <c r="A1075" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1075" t="n">
-        <v>1500</v>
+        <v>29000</v>
       </c>
       <c r="C1075" t="n">
-        <v>3.88000011444092</v>
+        <v>4.07999992370605</v>
       </c>
       <c r="D1075" t="n">
-        <v>3.8199999332428</v>
+        <v>3.83999991416931</v>
       </c>
       <c r="E1075" t="n">
-        <v>3.8199999332428</v>
+        <v>4.07999992370605</v>
       </c>
       <c r="F1075" t="n">
-        <v>3.88000011444092</v>
+        <v>3.83999991416931</v>
       </c>
       <c r="G1075" t="s">
         <v>7</v>
@@ -25099,22 +25099,22 @@
     </row>
     <row r="1076">
       <c r="A1076" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1076" t="n">
-        <v>11000</v>
+        <v>1500</v>
       </c>
       <c r="C1076" t="n">
-        <v>4</v>
+        <v>3.88000011444092</v>
       </c>
       <c r="D1076" t="n">
-        <v>3.90000009536743</v>
+        <v>3.8199999332428</v>
       </c>
       <c r="E1076" t="n">
-        <v>3.90000009536743</v>
+        <v>3.8199999332428</v>
       </c>
       <c r="F1076" t="n">
-        <v>4</v>
+        <v>3.88000011444092</v>
       </c>
       <c r="G1076" t="s">
         <v>7</v>
@@ -25122,22 +25122,22 @@
     </row>
     <row r="1077">
       <c r="A1077" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1077" t="n">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="C1077" t="n">
-        <v>4.1399998664856</v>
+        <v>4</v>
       </c>
       <c r="D1077" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E1077" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F1077" t="n">
         <v>4</v>
-      </c>
-      <c r="E1077" t="n">
-        <v>4</v>
-      </c>
-      <c r="F1077" t="n">
-        <v>4.05999994277954</v>
       </c>
       <c r="G1077" t="s">
         <v>7</v>
@@ -25145,19 +25145,19 @@
     </row>
     <row r="1078">
       <c r="A1078" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1078" t="n">
-        <v>2500</v>
+        <v>9500</v>
       </c>
       <c r="C1078" t="n">
-        <v>4.07999992370605</v>
+        <v>4.1399998664856</v>
       </c>
       <c r="D1078" t="n">
         <v>4</v>
       </c>
       <c r="E1078" t="n">
-        <v>4.01999998092651</v>
+        <v>4</v>
       </c>
       <c r="F1078" t="n">
         <v>4.05999994277954</v>
@@ -25168,22 +25168,22 @@
     </row>
     <row r="1079">
       <c r="A1079" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1079" t="n">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="C1079" t="n">
-        <v>4.09999990463257</v>
+        <v>4.07999992370605</v>
       </c>
       <c r="D1079" t="n">
-        <v>4.01999998092651</v>
+        <v>4</v>
       </c>
       <c r="E1079" t="n">
         <v>4.01999998092651</v>
       </c>
       <c r="F1079" t="n">
-        <v>4.09999990463257</v>
+        <v>4.05999994277954</v>
       </c>
       <c r="G1079" t="s">
         <v>7</v>
@@ -25191,22 +25191,22 @@
     </row>
     <row r="1080">
       <c r="A1080" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1080" t="n">
-        <v>17000</v>
+        <v>1000</v>
       </c>
       <c r="C1080" t="n">
         <v>4.09999990463257</v>
       </c>
       <c r="D1080" t="n">
-        <v>3.90000009536743</v>
+        <v>4.01999998092651</v>
       </c>
       <c r="E1080" t="n">
-        <v>4.07999992370605</v>
+        <v>4.01999998092651</v>
       </c>
       <c r="F1080" t="n">
-        <v>3.90000009536743</v>
+        <v>4.09999990463257</v>
       </c>
       <c r="G1080" t="s">
         <v>7</v>
@@ -25214,22 +25214,22 @@
     </row>
     <row r="1081">
       <c r="A1081" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1081" t="n">
-        <v>2000</v>
+        <v>17000</v>
       </c>
       <c r="C1081" t="n">
-        <v>4</v>
+        <v>4.09999990463257</v>
       </c>
       <c r="D1081" t="n">
-        <v>3.96000003814697</v>
+        <v>3.90000009536743</v>
       </c>
       <c r="E1081" t="n">
-        <v>3.96000003814697</v>
+        <v>4.07999992370605</v>
       </c>
       <c r="F1081" t="n">
-        <v>4</v>
+        <v>3.90000009536743</v>
       </c>
       <c r="G1081" t="s">
         <v>7</v>
@@ -25237,24 +25237,47 @@
     </row>
     <row r="1082">
       <c r="A1082" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1082" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="C1082" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1082" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="E1082" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="F1082" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1082" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1083" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C1083" t="n">
+        <v>4.15999984741211</v>
+      </c>
+      <c r="D1083" t="n">
+        <v>3.94000005722046</v>
+      </c>
+      <c r="E1083" t="n">
+        <v>4.15999984741211</v>
+      </c>
+      <c r="F1083" t="n">
         <v>4.09999990463257</v>
       </c>
-      <c r="D1082" t="n">
-        <v>4.09999990463257</v>
-      </c>
-      <c r="E1082" t="n">
-        <v>4.09999990463257</v>
-      </c>
-      <c r="F1082" t="n">
-        <v>4.09999990463257</v>
-      </c>
-      <c r="G1082" t="s">
+      <c r="G1083" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BELL.MI.xlsx
+++ b/data/BELL.MI.xlsx
@@ -28585,6 +28585,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1086">
+      <c r="A1086" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1086" t="n">
+        <v>10500</v>
+      </c>
+      <c r="C1086" t="n">
+        <v>4.19999980926514</v>
+      </c>
+      <c r="D1086" t="n">
+        <v>4.1399998664856</v>
+      </c>
+      <c r="E1086" t="n">
+        <v>4.15999984741211</v>
+      </c>
+      <c r="F1086" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="G1086" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="H1086" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BELL.MI.xlsx
+++ b/data/BELL.MI.xlsx
@@ -28596,7 +28596,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="D1086" t="n">
-        <v>4.1399998664856</v>
+        <v>4.09999990463257</v>
       </c>
       <c r="E1086" t="n">
         <v>4.15999984741211</v>
@@ -28608,6 +28608,32 @@
         <v>4.09999990463257</v>
       </c>
       <c r="H1086" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1087" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C1087" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="D1087" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="E1087" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="F1087" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="G1087" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="H1087" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BELL.MI.xlsx
+++ b/data/BELL.MI.xlsx
@@ -28619,7 +28619,7 @@
         <v>9000</v>
       </c>
       <c r="C1087" t="n">
-        <v>4.38000011444092</v>
+        <v>4.40000009536743</v>
       </c>
       <c r="D1087" t="n">
         <v>4.11999988555908</v>
@@ -28634,6 +28634,32 @@
         <v>4.40000009536743</v>
       </c>
       <c r="H1087" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1088" t="n">
+        <v>17500</v>
+      </c>
+      <c r="C1088" t="n">
+        <v>4.46000003814697</v>
+      </c>
+      <c r="D1088" t="n">
+        <v>4.23999977111816</v>
+      </c>
+      <c r="E1088" t="n">
+        <v>4.32000017166138</v>
+      </c>
+      <c r="F1088" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="G1088" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="H1088" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BELL.MI.xlsx
+++ b/data/BELL.MI.xlsx
@@ -28663,6 +28663,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1089">
+      <c r="A1089" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1089" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C1089" t="n">
+        <v>4.51999998092651</v>
+      </c>
+      <c r="D1089" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="E1089" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="F1089" t="n">
+        <v>4.51999998092651</v>
+      </c>
+      <c r="G1089" t="n">
+        <v>4.51999998092651</v>
+      </c>
+      <c r="H1089" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BELL.MI.xlsx
+++ b/data/BELL.MI.xlsx
@@ -28741,6 +28741,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1092">
+      <c r="A1092" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1092" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C1092" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D1092" t="n">
+        <v>4.46000003814697</v>
+      </c>
+      <c r="E1092" t="n">
+        <v>4.46000003814697</v>
+      </c>
+      <c r="F1092" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G1092" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H1092" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BELL.MI.xlsx
+++ b/data/BELL.MI.xlsx
@@ -25550,8 +25550,31 @@
       <c r="E1095" t="n">
         <v>4.5</v>
       </c>
-      <c r="F1095"/>
+      <c r="F1095" t="n">
+        <v>4.59999990463257</v>
+      </c>
       <c r="G1095" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1096" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C1096" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1096" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="E1096" t="n">
+        <v>4.65999984741211</v>
+      </c>
+      <c r="F1096"/>
+      <c r="G1096" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BELL.MI.xlsx
+++ b/data/BELL.MI.xlsx
@@ -25573,8 +25573,31 @@
       <c r="E1096" t="n">
         <v>4.65999984741211</v>
       </c>
-      <c r="F1096"/>
+      <c r="F1096" t="n">
+        <v>4.80000019073486</v>
+      </c>
       <c r="G1096" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1097" t="n">
+        <v>17500</v>
+      </c>
+      <c r="C1097" t="n">
+        <v>4.88000011444092</v>
+      </c>
+      <c r="D1097" t="n">
+        <v>4.6399998664856</v>
+      </c>
+      <c r="E1097" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1097"/>
+      <c r="G1097" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BELL.MI.xlsx
+++ b/data/BELL.MI.xlsx
@@ -25596,8 +25596,31 @@
       <c r="E1097" t="n">
         <v>4.80000019073486</v>
       </c>
-      <c r="F1097"/>
+      <c r="F1097" t="n">
+        <v>4.76000022888184</v>
+      </c>
       <c r="G1097" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1098" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C1098" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1098" t="n">
+        <v>4.69999980926514</v>
+      </c>
+      <c r="E1098" t="n">
+        <v>4.73999977111816</v>
+      </c>
+      <c r="F1098"/>
+      <c r="G1098" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BELL.MI.xlsx
+++ b/data/BELL.MI.xlsx
@@ -25619,8 +25619,31 @@
       <c r="E1098" t="n">
         <v>4.73999977111816</v>
       </c>
-      <c r="F1098"/>
+      <c r="F1098" t="n">
+        <v>4.71999979019165</v>
+      </c>
       <c r="G1098" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1099" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1099" t="n">
+        <v>4.90000009536743</v>
+      </c>
+      <c r="D1099" t="n">
+        <v>4.82000017166138</v>
+      </c>
+      <c r="E1099" t="n">
+        <v>4.82000017166138</v>
+      </c>
+      <c r="F1099"/>
+      <c r="G1099" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BELL.MI.xlsx
+++ b/data/BELL.MI.xlsx
@@ -25649,6 +25649,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1100">
+      <c r="A1100" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1100" t="n">
+        <v>13500</v>
+      </c>
+      <c r="C1100" t="n">
+        <v>4.92000007629395</v>
+      </c>
+      <c r="D1100" t="n">
+        <v>4.82000017166138</v>
+      </c>
+      <c r="E1100" t="n">
+        <v>4.90000009536743</v>
+      </c>
+      <c r="F1100" t="n">
+        <v>4.88000011444092</v>
+      </c>
+      <c r="G1100" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BELL.MI.xlsx
+++ b/data/BELL.MI.xlsx
@@ -29012,7 +29012,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="D1102" t="n">
-        <v>4.78000020980835</v>
+        <v>4.76000022888184</v>
       </c>
       <c r="E1102" t="n">
         <v>4.78000020980835</v>
@@ -29024,6 +29024,32 @@
         <v>4.76000022888184</v>
       </c>
       <c r="H1102" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1103" t="n">
+        <v>500</v>
+      </c>
+      <c r="C1103" t="n">
+        <v>4.69999980926514</v>
+      </c>
+      <c r="D1103" t="n">
+        <v>4.69999980926514</v>
+      </c>
+      <c r="E1103" t="n">
+        <v>4.69999980926514</v>
+      </c>
+      <c r="F1103" t="n">
+        <v>4.69999980926514</v>
+      </c>
+      <c r="G1103" t="n">
+        <v>4.69999980926514</v>
+      </c>
+      <c r="H1103" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BELL.MI.xlsx
+++ b/data/BELL.MI.xlsx
@@ -29053,6 +29053,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1104">
+      <c r="A1104" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1104" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C1104" t="n">
+        <v>4.76000022888184</v>
+      </c>
+      <c r="D1104" t="n">
+        <v>4.65999984741211</v>
+      </c>
+      <c r="E1104" t="n">
+        <v>4.65999984741211</v>
+      </c>
+      <c r="F1104" t="n">
+        <v>4.76000022888184</v>
+      </c>
+      <c r="G1104" t="n">
+        <v>4.76000022888184</v>
+      </c>
+      <c r="H1104" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BELL.MI.xlsx
+++ b/data/BELL.MI.xlsx
@@ -32423,6 +32423,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1106">
+      <c r="A1106" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1106" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1106" t="n">
+        <v>4.65999984741211</v>
+      </c>
+      <c r="D1106" t="n">
+        <v>4.78000020980835</v>
+      </c>
+      <c r="E1106" t="n">
+        <v>4.34000015258789</v>
+      </c>
+      <c r="F1106" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G1106" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H1106" t="n">
+        <v>22000</v>
+      </c>
+      <c r="I1106" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BELL.MI.xlsx
+++ b/data/BELL.MI.xlsx
@@ -32452,6 +32452,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1107">
+      <c r="A1107" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1107" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1107" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="D1107" t="n">
+        <v>4.42000007629395</v>
+      </c>
+      <c r="E1107" t="n">
+        <v>4.34000015258789</v>
+      </c>
+      <c r="F1107" t="n">
+        <v>4.42000007629395</v>
+      </c>
+      <c r="G1107" t="n">
+        <v>4.42000007629395</v>
+      </c>
+      <c r="H1107" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I1107" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BELL.MI.xlsx
+++ b/data/BELL.MI.xlsx
@@ -32481,6 +32481,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1108">
+      <c r="A1108" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1108" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1108" t="n">
+        <v>4.3600001335144</v>
+      </c>
+      <c r="D1108" t="n">
+        <v>4.48000001907349</v>
+      </c>
+      <c r="E1108" t="n">
+        <v>4.34000015258789</v>
+      </c>
+      <c r="F1108" t="n">
+        <v>4.42000007629395</v>
+      </c>
+      <c r="G1108" t="n">
+        <v>4.42000007629395</v>
+      </c>
+      <c r="H1108" t="n">
+        <v>15500</v>
+      </c>
+      <c r="I1108" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BELL.MI.xlsx
+++ b/data/BELL.MI.xlsx
@@ -32510,6 +32510,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1109">
+      <c r="A1109" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1109" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1109" t="n">
+        <v>4.32000017166138</v>
+      </c>
+      <c r="D1109" t="n">
+        <v>4.42000007629395</v>
+      </c>
+      <c r="E1109" t="n">
+        <v>3.92000007629395</v>
+      </c>
+      <c r="F1109" t="n">
+        <v>4.03999996185303</v>
+      </c>
+      <c r="G1109" t="n">
+        <v>4.03999996185303</v>
+      </c>
+      <c r="H1109" t="n">
+        <v>21000</v>
+      </c>
+      <c r="I1109" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BELL.MI.xlsx
+++ b/data/BELL.MI.xlsx
@@ -32539,6 +32539,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1110">
+      <c r="A1110" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1110" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1110" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="D1110" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="E1110" t="n">
+        <v>4.03999996185303</v>
+      </c>
+      <c r="F1110" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="G1110" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="H1110" t="n">
+        <v>13000</v>
+      </c>
+      <c r="I1110" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BELL.MI.xlsx
+++ b/data/BELL.MI.xlsx
@@ -32568,6 +32568,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1111">
+      <c r="A1111" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1111" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1111" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="D1111" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E1111" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="F1111" t="n">
+        <v>4.48000001907349</v>
+      </c>
+      <c r="G1111" t="n">
+        <v>4.48000001907349</v>
+      </c>
+      <c r="H1111" t="n">
+        <v>14000</v>
+      </c>
+      <c r="I1111" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BELL.MI.xlsx
+++ b/data/BELL.MI.xlsx
@@ -32597,6 +32597,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1112">
+      <c r="A1112" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1112" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1112" t="n">
+        <v>4.48000001907349</v>
+      </c>
+      <c r="D1112" t="n">
+        <v>4.78000020980835</v>
+      </c>
+      <c r="E1112" t="n">
+        <v>4.48000001907349</v>
+      </c>
+      <c r="F1112" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="G1112" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="H1112" t="n">
+        <v>21000</v>
+      </c>
+      <c r="I1112" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BELL.MI.xlsx
+++ b/data/BELL.MI.xlsx
@@ -32626,6 +32626,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1113">
+      <c r="A1113" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1113" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1113" t="n">
+        <v>4.84000015258789</v>
+      </c>
+      <c r="D1113" t="n">
+        <v>4.90000009536743</v>
+      </c>
+      <c r="E1113" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="F1113" t="n">
+        <v>4.76000022888184</v>
+      </c>
+      <c r="G1113" t="n">
+        <v>4.76000022888184</v>
+      </c>
+      <c r="H1113" t="n">
+        <v>18000</v>
+      </c>
+      <c r="I1113" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BELL.MI.xlsx
+++ b/data/BELL.MI.xlsx
@@ -32655,6 +32655,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1114">
+      <c r="A1114" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1114" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1114" t="n">
+        <v>4.76000022888184</v>
+      </c>
+      <c r="D1114" t="n">
+        <v>4.90000009536743</v>
+      </c>
+      <c r="E1114" t="n">
+        <v>4.65999984741211</v>
+      </c>
+      <c r="F1114" t="n">
+        <v>4.65999984741211</v>
+      </c>
+      <c r="G1114" t="n">
+        <v>4.65999984741211</v>
+      </c>
+      <c r="H1114" t="n">
+        <v>18500</v>
+      </c>
+      <c r="I1114" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
